--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.55906667064528</v>
+        <v>2.365848333979857</v>
       </c>
       <c r="D2" t="n">
-        <v>14.69091668377422</v>
+        <v>2.38727396111331</v>
       </c>
       <c r="E2" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F2" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.25577031732644</v>
+        <v>1.829062676565547</v>
       </c>
       <c r="D3" t="n">
-        <v>12.12241269881622</v>
+        <v>1.969892063557636</v>
       </c>
       <c r="E3" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F3" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.4899766823419</v>
+        <v>7.554621210880558</v>
       </c>
       <c r="D4" t="n">
-        <v>46.0349324759814</v>
+        <v>7.480676527346978</v>
       </c>
       <c r="E4" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F4" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.91712735790314</v>
+        <v>2.42403319565926</v>
       </c>
       <c r="D5" t="n">
-        <v>14.19057769702092</v>
+        <v>2.305968875765899</v>
       </c>
       <c r="E5" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F5" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.44648187112671</v>
+        <v>7.060053304058092</v>
       </c>
       <c r="D6" t="n">
-        <v>43.34316107767581</v>
+        <v>7.043263675122319</v>
       </c>
       <c r="E6" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F6" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.34887487095835</v>
+        <v>3.144192166530732</v>
       </c>
       <c r="D7" t="n">
-        <v>18.65989726840373</v>
+        <v>3.032233306115606</v>
       </c>
       <c r="E7" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F7" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.28878522442984</v>
+        <v>1.99692759896985</v>
       </c>
       <c r="D8" t="n">
-        <v>11.55684504604084</v>
+        <v>1.877987319981637</v>
       </c>
       <c r="E8" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F8" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.15881319946731</v>
+        <v>3.275807144913438</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85615120550247</v>
+        <v>3.226624570894152</v>
       </c>
       <c r="E9" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F9" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.47876695807711</v>
+        <v>4.140299630687529</v>
       </c>
       <c r="D10" t="n">
-        <v>24.57028289252526</v>
+        <v>3.992670970035355</v>
       </c>
       <c r="E10" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F10" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>56.84395132212131</v>
+        <v>9.237142089844713</v>
       </c>
       <c r="D11" t="n">
-        <v>56.97143457157154</v>
+        <v>9.257858117880374</v>
       </c>
       <c r="E11" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F11" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.35363152036642</v>
+        <v>5.094965122059543</v>
       </c>
       <c r="D12" t="n">
-        <v>31.7869384544626</v>
+        <v>5.165377498850173</v>
       </c>
       <c r="E12" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F12" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.60428507174456</v>
+        <v>3.835696324158491</v>
       </c>
       <c r="D13" t="n">
-        <v>48.69680491890339</v>
+        <v>7.913230799321801</v>
       </c>
       <c r="E13" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F13" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.23522627176205</v>
+        <v>1.988224269161333</v>
       </c>
       <c r="D14" t="n">
-        <v>12.88040518054457</v>
+        <v>2.093065841838492</v>
       </c>
       <c r="E14" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F14" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.36231677218948</v>
+        <v>6.55887647548079</v>
       </c>
       <c r="D15" t="n">
-        <v>40.68429550133062</v>
+        <v>6.611198018966226</v>
       </c>
       <c r="E15" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F15" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>44.08357397913752</v>
+        <v>7.163580771609847</v>
       </c>
       <c r="D16" t="n">
-        <v>44.58370238904833</v>
+        <v>7.244851638220354</v>
       </c>
       <c r="E16" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F16" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5.830502751473214</v>
+        <v>0.9474566971143974</v>
       </c>
       <c r="D17" t="n">
-        <v>45.9294397937355</v>
+        <v>7.463533966482019</v>
       </c>
       <c r="E17" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F17" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>15.11621645783097</v>
+        <v>2.456385174397533</v>
       </c>
       <c r="D18" t="n">
-        <v>64.03799802681539</v>
+        <v>10.4061746793575</v>
       </c>
       <c r="E18" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F18" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>28.88461877564006</v>
+        <v>4.693750551041511</v>
       </c>
       <c r="D19" t="n">
-        <v>72.98337766908875</v>
+        <v>11.85979887122692</v>
       </c>
       <c r="E19" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F19" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>38.68535790321414</v>
+        <v>6.286370659272298</v>
       </c>
       <c r="D20" t="n">
-        <v>50.20156863029099</v>
+        <v>8.157754902422287</v>
       </c>
       <c r="E20" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F20" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>23.0599495556204</v>
+        <v>3.747241802788314</v>
       </c>
       <c r="D21" t="n">
-        <v>22.64179576701847</v>
+        <v>3.679291812140501</v>
       </c>
       <c r="E21" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F21" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>35.88117893319653</v>
+        <v>5.830691576644436</v>
       </c>
       <c r="D22" t="n">
-        <v>35.44396365197928</v>
+        <v>5.759644093446633</v>
       </c>
       <c r="E22" t="n">
-        <v>13.72524316045993</v>
+        <v>2.230352013574738</v>
       </c>
       <c r="F22" t="n">
-        <v>17.99205029896027</v>
+        <v>2.923708173581044</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
